--- a/docs/templates/3d-home-academy-catalog-template.xlsx
+++ b/docs/templates/3d-home-academy-catalog-template.xlsx
@@ -14,6 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Комплектации" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поставщики" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расходники" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Категории" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объекты" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Позиции объектов" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -472,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Товары, Цены, Работы, Комплектации, Поставщики, Расходники</t>
+          <t>Товары, Цены, Работы, Комплектации, Поставщики, Расходники, Категории, Объекты, Позиции объектов</t>
         </is>
       </c>
     </row>
@@ -535,6 +538,777 @@
         <is>
           <t>Подтверждённые заказы хранят цены на момент оформления — изменение таблицы их не меняет.</t>
         </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>КОНСТРУКТОР: листы «Категории», «Объекты», «Позиции объектов».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Категории — разделы левого меню (category_id, name, icon, order).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Объекты — типы объектов квартиры: type_id, category_id, name, renderer (door|entrance|window|wall|none), placement (door|entrance|window|room_walls), primary_slot, description, lesson_steps (шаги через |), mistakes (через |).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Позиции объектов — состав объекта: type_id, slot, label, qty (норма), per (pcs|opening_m2|opening_w|opening_h|opening_perimeter_m|wall_m2|floor_m2|perimeter_m|ceiling_m2), waste (запас, 0.1 = 10%), optional (1/0), default_product_id, work_id, work_per, order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Товар может переопределить норму позиции в attrs: rate=0.1;per=wall_m2;waste=0.15;work=W-WL-WP (например, обои — рулоны на м²).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Новая модель двери или цвет краски = строка в «Товары» с тем же slot + строка в «Цены». Новый тип объекта = строка в «Объекты» + его позиции. Код не меняется.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>per</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>waste</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>default_product_id</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>work_id</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>work_per</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Полотно</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DR-NEO-WHITE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>W-DR-INST</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>door.frame</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Коробка</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>DR-FRAME-STD</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>door.casing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Наличник (с двух сторон)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>opening_perimeter_m</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DR-CAS-70</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>door.hinges</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Петли</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DR-HNG-BUTT</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>door.handle</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ручка</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DR-HDL-CHROME</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>door.latch</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Защёлка / фиксатор</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DR-LCH-MAG</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>entr.door</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Дверной блок</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ENT-STEEL-GREY</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>W-ENT-INST</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>entr.lock</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Дополнительный замок</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>W-ENT-LOCK</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>entr.reveal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Откосы</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>opening_perimeter_m</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ENT-REV-MDF</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>W-ENT-REVEAL</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>opening_perimeter_m</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>win.unit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Окно (профиль + стеклопакет)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>opening_m2</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>WIN-PVC-WHITE</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>W-WIN-INST</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>opening_m2</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>win.sill</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Подоконник</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>opening_w</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>WIN-SILL-PVC</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>W-WIN-SILL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>opening_w</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>win.reveal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Откосы</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>opening_perimeter_m</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>WIN-REV-PVC</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>W-WIN-REV</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>opening_perimeter_m</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Финишная отделка</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>wall_m2</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>WL-PNT-WHITE</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>W-WL-PAINT</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>wall_m2</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>wall.primer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Грунт</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>wall_m2</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>WL-PRIMER</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>W-WL-PRIME</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>wall_m2</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -548,24 +1322,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="51" customWidth="1" min="5" max="5"/>
     <col width="59" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -3640,6 +4414,2842 @@
         </is>
       </c>
       <c r="P41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DR-NEO-WHITE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Дверь «Нео» гладкая, белая эмаль</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Минималистичная дверь для любого интерьера</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Покрытие=эмаль;Наполнение=сотовое;Размер=800×2000 мм;Толщина (мм)=38</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>style=flat;color=#f2f0eb;model=Нео;tier=econom</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Каркас из бруса с сотовым наполнением, облицован МДФ и окрашен эмалью</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>12</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Протирать влажной тканью без абразива</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>DEMO-DR-NEO-W</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DR-NEO-GRAPHITE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Дверь «Нео» гладкая, графит</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Тёмная дверь для контрастного интерьера</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Покрытие=эмаль;Наполнение=сотовое;Размер=800×2000 мм;Толщина (мм)=38</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>style=flat;color=#4b4e53;model=Нео</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Каркас из бруса с сотовым наполнением, облицован МДФ и окрашен эмалью</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>12</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Протирать влажной тканью без абразива</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>DEMO-DR-NEO-G</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DR-LINE-OAK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Дверь «Лайн» с фрезеровкой, дуб</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Тёплый древесный оттенок, горизонтальные линии</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Покрытие=экошпон;Наполнение=ДСП трубчатое;Размер=800×2000 мм;Шумоизоляция=улучшенная</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>style=grooves;color=#b5895d;model=Лайн;tier=comfort</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Трубчатая ДСП внутри даёт вес и лучшую шумоизоляцию, чем соты</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>24</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Влажная уборка; избегать прямого попадания воды</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>DEMO-DR-LINE</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DR-VISTA-GLASS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Дверь «Виста» со стеклом сатинато</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Пропускает свет в тёмную прихожую или коридор</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Покрытие=экошпон;Стекло=сатинато 4 мм;Размер=800×2000 мм</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>style=glass;color=#e8e2d8;model=Виста</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Матовое закалённое стекло рассеивает свет и скрывает силуэты</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>24</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Стекло — средство для стёкол; полотно — влажная ткань</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>DEMO-DR-VISTA</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DR-CLASSIC-IVORY</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Дверь «Классика» филёнчатая, слоновая кость</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Классический интерьер, массив сосны</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Материал=массив сосны;Покрытие=эмаль;Филёнки=4;Размер=800×2000 мм</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>style=panel;color=#efe5cf;model=Классика;tier=premium</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Цельная древесина с филёнками: тяжёлая, тихая, ремонтопригодная</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>36</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Мягкая влажная уборка; подкрашивается</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>DEMO-DR-CLASSIC</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DR-LOFT-BLACK</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Дверь «Лофт» в раскладку, чёрный</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Индустриальный стиль, много света</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Профиль=алюминий;Стекло=прозрачное закалённое;Размер=800×2000 мм</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>style=loft;color=#26282b;model=Лофт</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Алюминиевая рамка с закалённым стеклом в раскладке</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>24</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Средство для стёкол</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>DEMO-DR-LOFT</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DR-FRAME-STD</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>door.frame</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Коробка МДФ телескопическая</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Стандартная коробка под наличник</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Материал=МДФ;Глубина (мм)=75;Регулировка=телескоп</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Телескопический паз позволяет подогнать наличник и добор без зазоров</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>12</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>DEMO-DR-FR</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DR-FRAME-HIDDEN</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>door.frame</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Скрытая алюминиевая коробка (инвизибл)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Дверь в одной плоскости со стеной, без наличников</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Материал=алюминий;Под покраску=да</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>hidden=1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Коробка замоноличивается в стену и шпаклюется — наличники не нужны</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>60</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>DEMO-DR-FRH</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DR-CAS-70</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>door.casing</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Наличник плоский 70 мм</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Закрывает монтажный шов вокруг коробки</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Ширина (мм)=70;Длина планки (м)=2.2</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Наличник скрывает пену и неровности между коробкой и стеной</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>12</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>DEMO-DR-CAS70</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DR-CAS-90-CLASSIC</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>door.casing</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Наличник фигурный 90 мм</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Для классических дверей</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Ширина (мм)=90;Профиль=фигурный</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Фигурный профиль поддерживает рисунок филёнчатой двери</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>12</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>DEMO-DR-CAS90</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DR-HNG-BUTT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>door.hinges</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Петля накладная «бабочка»</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Без врезки, быстрый монтаж</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Нагрузка (кг)=40;Врезка=не нужна</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Петля складывается и не требует паза в полотне и коробке</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>12</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Смазывать раз в год</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>DEMO-DR-HB</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DR-HNG-HIDDEN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>door.hinges</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Петля скрытая 3D-регулируемая</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Не видна при закрытой двери</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Нагрузка (кг)=60;Регулировка=3D</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Петля прячется в торце полотна и регулируется в трёх плоскостях</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>60</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Подтягивать регулировку по необходимости</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>DEMO-DR-HH</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DR-HDL-CHROME</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>door.handle</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ручка на розетке, матовый хром</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Универсальная ручка</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Материал=ЦАМ;Покрытие=матовый хром</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>handle=#c4c7cb</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Розетка крепится стяжками сквозь полотно, ручка нажимает язычок защёлки</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>24</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>DEMO-DR-HC</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DR-HDL-BLACK</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>door.handle</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ручка на розетке, чёрный матовый</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Для светлых и тёмных дверей</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Материал=ЦАМ;Покрытие=чёрный матовый</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>handle=#1c1d1f</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Розетка крепится стяжками сквозь полотно, ручка нажимает язычок защёлки</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>24</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>DEMO-DR-HBK</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DR-HDL-BRASS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>door.handle</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Ручка классическая, латунь</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Для классического интерьера</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Материал=латунь</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>handle=#c39b4a</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Массивная латунная ручка на розетке</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>36</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Полировать мягкой тканью</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>DEMO-DR-HBR</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DR-LCH-MAG</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>door.latch</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Защёлка магнитная бесшумная</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Дверь закрывается тихо</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Тип=магнитная</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Магнит в ответной планке притягивает язычок только у закрытой двери</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>24</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>DEMO-DR-LM</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DR-LCH-WC</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>door.latch</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Защёлка с фиксатором WC</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Для санузла и ванной</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Тип=с фиксатором;Поворотник=WC</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Поворотник блокирует ручку изнутри, снаружи открывается монетой</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>24</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>DEMO-DR-LW</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ENT-STEEL-GREY</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>entr.door</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Входная дверь стальная, антик серебро</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Базовая защита и шумоизоляция</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Сталь (мм)=1.5;Замки=2 (II класс);Утеплитель=минвата;Размер=900×2050 мм</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>style=steel;color=#6c7077;model=Сталь;tier=econom</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Стальное полотно на рёбрах жёсткости, два замка разных типов</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>24</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Смазывать замки раз в год</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>DEMO-ENT-S</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ENT-THERMO-WOOD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>entr.door</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Входная дверь с терморазрывом, панель «орех»</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Для двери на улицу или холодный тамбур</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Сталь (мм)=2;Терморазрыв=да;Замки=2 (III–IV класс);Размер=900×2050 мм</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>style=panel;color=#5a3d2a;model=Термо;tier=premium</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Терморазрыв разделяет внешний и внутренний лист — нет промерзания и конденсата</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>60</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Смазывать замки и уплотнитель раз в год</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>DEMO-ENT-T</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ENT-MODERN-WHITE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>entr.door</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Входная дверь «Модерн», белый матовый</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Светлая дверь в современный интерьер</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Сталь (мм)=1.8;Замки=2 (III класс);Панель=МДФ 10 мм;Размер=900×2050 мм</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>style=flat;color=#ebe9e4;model=Модерн;tier=comfort</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>МДФ-панели защищают металл и выравнивают внешний вид</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>36</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Влажная уборка</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>DEMO-ENT-M</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ENT-LOCK-ADD</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>entr.lock</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Дополнительный цилиндровый замок IV класса</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ещё один контур защиты</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Класс=IV;Ключи=5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Второй замок другого типа усложняет вскрытие</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>24</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>DEMO-ENT-L</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ENT-REV-MDF</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>entr.reveal</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Откос МДФ под цвет двери</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Закрывает проём изнутри</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Ширина (мм)=до 250</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Панель МДФ на каркасе закрывает неровный проём</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>12</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>DEMO-ENT-R</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WIN-PVC-WHITE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>win.unit</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Окно ПВХ 5 камер, двухкамерный стеклопакет, белое</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Тёплое окно для жилой комнаты</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Профиль=5 камер, 70 мм;Стеклопакет=4-10-4-10-4;Фурнитура=поворотно-откидная</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>color=#f7f7f4;model=ПВХ;tier=econom</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Камеры профиля и воздушные прослойки стеклопакета снижают теплопотери</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>60</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Смазывать фурнитуру раз в год</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>SUP-WIN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>DEMO-WIN-W</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WIN-PVC-ANTH</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>win.unit</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Окно ПВХ ламинированное, антрацит</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Современный вид снаружи и внутри</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Профиль=6 камер, 80 мм;Стеклопакет=энергосберегающий;Ламинация=антрацит</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>color=#3b3e44;model=ПВХ;tier=comfort</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Энергосберегающее напыление отражает тепло обратно в комнату</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>60</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Смазывать фурнитуру раз в год</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>SUP-WIN</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>DEMO-WIN-A</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WIN-ALU-WOOD</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>win.unit</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Окно тёплый алюминий, отделка «дерево»</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Узкие рамы и максимум света</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Профиль=алюминий с терморазрывом;Стеклопакет=энергосберегающий 2-камерный</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>color=#8a6243;model=Алюминий;tier=premium</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Терморазрыв из полиамида разделяет внутренний и внешний алюминий</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>120</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Смазывать фурнитуру раз в год</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SUP-WIN</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>DEMO-WIN-AW</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WIN-SILL-PVC</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>win.sill</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Подоконник ПВХ 300 мм, белый</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Практичный подоконник</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Ширина (мм)=300</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Полая панель ПВХ не боится влаги</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>60</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>SUP-WIN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>DEMO-WIN-SP</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WIN-SILL-STONE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>win.sill</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Подоконник из искусственного камня</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Прочный и красивый</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Ширина (мм)=300;Материал=акриловый камень</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Литой камень без швов, выдерживает горячее</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>120</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>SUP-WIN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>DEMO-WIN-SS</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WIN-REV-PVC</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>win.reveal</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Откос ПВХ-панель</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Чистовая отделка проёма</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>3</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Ширина (мм)=до 300</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Сэндвич-панель закрывает монтажный шов и утепляет откос</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>60</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>SUP-WIN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>DEMO-WIN-R</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>WL-PNT-WHITE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Краска интерьерная моющаяся, белая</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Универсальная отделка стен</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>9</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Блеск=глубокоматовая;Класс мытья=2;Расход (л/м², 2 слоя)=0.25</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>finish=paint;color=#f3f1ec;rate=0.25;model=Краска;tier=econom</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Акриловая краска образует плёнку, которую можно мыть</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Мыть мягкой губкой</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>DEMO-WL-PW</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WL-PNT-SAGE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Краска интерьерная, шалфей</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Спокойный зелёный оттенок</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>9</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Блеск=матовая;Класс мытья=2;Расход (л/м², 2 слоя)=0.25</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>finish=paint;color=#a9b6a0;rate=0.25;model=Краска</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Колеровка в базу А по веерному каталогу</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Мыть мягкой губкой</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>DEMO-WL-PS</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WL-PNT-SAND</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Краска интерьерная, песок</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Тёплый нейтральный тон</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>9</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Блеск=матовая;Класс мытья=2;Расход (л/м², 2 слоя)=0.25</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>finish=paint;color=#dccbad;rate=0.25;model=Краска;tier=comfort</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Колеровка в базу А по веерному каталогу</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Мыть мягкой губкой</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>DEMO-WL-PD</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WL-PNT-GRAPHITE</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Краска интерьерная, графит</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Акцентная стена</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>9</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Блеск=глубокоматовая;Класс мытья=1;Расход (л/м², 2 слоя)=0.27</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>finish=paint;color=#5d6167;rate=0.27;model=Краска</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Колеровка в базу С; тёмные цвета требуют идеального основания</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Мыть мягкой губкой</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>DEMO-WL-PG</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>WL-PNT-TERRA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Краска интерьерная, терракота</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Тёплый акцент</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>9</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Блеск=матовая;Расход (л/м², 2 слоя)=0.26</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>finish=paint;color=#c4805f;rate=0.26;model=Краска</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Колеровка в базу С</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Мыть мягкой губкой</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>DEMO-WL-PT</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WL-WP-LINEN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Обои флизелиновые «Лён», рулон 1.06×10 м</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Фактура ткани, хорошо скрывают мелкие дефекты</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Основа=флизелин;Рулон=1.06×10 м;Раппорт=без подбора</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>finish=wallpaper;color=#e4d9c6;rate=0.1;work=W-WL-WP;model=Обои</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Флизелин не растягивается от клея — клей наносится на стену</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Сухая уборка</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>DEMO-WL-WP</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>WL-PLASTER-MICRO</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Декоративная штукатурка «микроцемент»</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Бесшовная фактурная поверхность</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>15</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Расход (кг/м²)=1.2;Слоёв=2 + лак</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>finish=plaster;color=#c8c2b7;rate=1.2;work=W-WL-PLASTER;model=Штукатурка;tier=premium</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Тонкий минеральный слой с лаком создаёт фактуру бетона</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Влажная уборка после лакировки</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>DEMO-WL-PL</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>WL-PANEL-BAMBOO</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Бамбуковые реечные панели</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Тёплый акцент и шумопоглощение</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Материал=бамбук на войлоке;Упаковка (м²)=2.88</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>finish=panel;color=#c6a172;rate=1;work=W-WL-PANEL;model=Панели</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Рейки на войлочной подложке клеятся и фиксируются саморезами</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>24</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Сухая уборка</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>DEMO-WL-BB</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WL-PRIMER</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>wall.primer</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Грунт глубокого проникновения</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Связывает основание, снижает расход финиша</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>10</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Расход (л/м²)=0.15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Грунт проникает в поры и выравнивает впитываемость</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>DEMO-WL-PR</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>WL-PNT-LIGHT</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Краска интерьерная базовая, светло-серая</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Недорогая отделка под сдачу</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>9</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Блеск=матовая;Класс мытья=3;Расход (л/м², 2 слоя)=0.25</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>finish=paint;color=#e9e8e4;rate=0.25;model=Краска;tier=econom</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Водно-дисперсионная краска для сухих помещений</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Сухая уборка</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>SUP-MAT</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>DEMO-WL-PL0</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3662,10 +7272,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -4820,6 +8430,1070 @@
         </is>
       </c>
       <c r="F41" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DR-NEO-WHITE</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C42" t="n">
+        <v>28000</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DR-NEO-GRAPHITE</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C43" t="n">
+        <v>29500</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DR-LINE-OAK</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C44" t="n">
+        <v>36000</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DR-VISTA-GLASS</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>31000</v>
+      </c>
+      <c r="C45" t="n">
+        <v>42000</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DR-CLASSIC-IVORY</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C46" t="n">
+        <v>55000</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DR-LOFT-BLACK</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46000</v>
+      </c>
+      <c r="C47" t="n">
+        <v>61000</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DR-FRAME-STD</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C48" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DR-FRAME-HIDDEN</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C49" t="n">
+        <v>38000</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DR-CAS-70</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>600</v>
+      </c>
+      <c r="C50" t="n">
+        <v>900</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DR-CAS-90-CLASSIC</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DR-HNG-BUTT</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DR-HNG-HIDDEN</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C53" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DR-HDL-CHROME</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C54" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DR-HDL-BLACK</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>5200</v>
+      </c>
+      <c r="C55" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DR-HDL-BRASS</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C56" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DR-LCH-MAG</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DR-LCH-WC</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4600</v>
+      </c>
+      <c r="C58" t="n">
+        <v>6500</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ENT-STEEL-GREY</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C59" t="n">
+        <v>145000</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ENT-THERMO-WOOD</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>180000</v>
+      </c>
+      <c r="C60" t="n">
+        <v>230000</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ENT-MODERN-WHITE</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C61" t="n">
+        <v>195000</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ENT-LOCK-ADD</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C62" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ENT-REV-MDF</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WIN-PVC-WHITE</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C64" t="n">
+        <v>38000</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WIN-PVC-ANTH</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C65" t="n">
+        <v>52000</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WIN-ALU-WOOD</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>66000</v>
+      </c>
+      <c r="C66" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WIN-SILL-PVC</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C67" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WIN-SILL-STONE</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C68" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WIN-REV-PVC</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>WL-PNT-WHITE</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2300</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WL-PNT-SAGE</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3700</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WL-PNT-SAND</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3700</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WL-PNT-GRAPHITE</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4100</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>WL-PNT-TERRA</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3900</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WL-WP-LINEN</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C75" t="n">
+        <v>13500</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>WL-PLASTER-MICRO</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2600</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>WL-PANEL-BAMBOO</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C77" t="n">
+        <v>15500</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WL-PRIMER</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>900</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>WL-PNT-LIGHT</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>KZT</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>DEMO</t>
         </is>
@@ -4836,13 +9510,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -5366,6 +10040,486 @@
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>W-DR-INST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Установка межкомнатной двери под ключ (коробка, полотно, врезка фурнитуры, наличники)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>W-ENT-INST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>entr.door</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Установка входной двери с демонтажом старой</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>W-ENT-LOCK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>entr.lock</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Врезка дополнительного замка</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>W-ENT-REVEAL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>entr.reveal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Монтаж откосов входной двери</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>W-WIN-INST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>win.unit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Монтаж окна с монтажным швом по ГОСТ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>W-WIN-SILL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>win.sill</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Установка подоконника</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>W-WIN-REV</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>win.reveal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Монтаж откосов окна</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>W-WL-PAINT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Окраска стен в 2 слоя</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>W-WL-WP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Поклейка флизелиновых обоев</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>W-WL-PLASTER</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Нанесение декоративной штукатурки с лаком</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W-WL-PANEL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Монтаж реечных панелей</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>W-WL-PRIME</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wall.primer</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Грунтование стен</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>350</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>DEMO</t>
         </is>
@@ -5387,15 +10541,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6523,6 +11677,1134 @@
       <c r="F36" t="inlineStr">
         <is>
           <t>W-SH-BOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>KIT-DR-E</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DR-NEO-WHITE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>W-DR-INST</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>KIT-DR-E</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>door.frame</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DR-FRAME-STD</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>KIT-DR-E</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>door.casing</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DR-CAS-70</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>KIT-DR-E</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>door.hinges</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DR-HNG-BUTT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>KIT-DR-E</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>door.handle</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DR-HDL-CHROME</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>KIT-DR-C</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DR-LINE-OAK</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>W-DR-INST</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>KIT-DR-C</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>door.frame</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DR-FRAME-STD</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>KIT-DR-C</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>door.casing</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DR-CAS-70</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>KIT-DR-C</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>door.hinges</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DR-HNG-HIDDEN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KIT-DR-C</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>door.handle</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DR-HDL-BLACK</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>KIT-DR-C</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>door.latch</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DR-LCH-MAG</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>KIT-DR-P</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DR-CLASSIC-IVORY</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>W-DR-INST</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>KIT-DR-P</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>door.frame</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DR-FRAME-STD</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KIT-DR-P</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>door.casing</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DR-CAS-90-CLASSIC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>KIT-DR-P</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>door.hinges</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DR-HNG-HIDDEN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>KIT-DR-P</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>door.handle</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DR-HDL-BRASS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>KIT-DR-P</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>door.latch</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DR-LCH-MAG</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>KIT-ENT-E</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>entr.door</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ENT-STEEL-GREY</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>W-ENT-INST</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>KIT-ENT-C</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>entr.door</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ENT-MODERN-WHITE</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>W-ENT-INST</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>KIT-ENT-C</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>entr.reveal</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ENT-REV-MDF</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>W-ENT-REVEAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>KIT-ENT-P</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>entr.door</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ENT-THERMO-WOOD</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>W-ENT-INST</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KIT-ENT-P</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>entr.lock</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ENT-LOCK-ADD</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>W-ENT-LOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>KIT-ENT-P</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>entr.reveal</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ENT-REV-MDF</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>W-ENT-REVEAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>KIT-WIN-E</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>win.unit</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>WIN-PVC-WHITE</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>W-WIN-INST</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>KIT-WIN-E</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>win.sill</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>WIN-SILL-PVC</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>W-WIN-SILL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>KIT-WIN-C</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>win.unit</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>WIN-PVC-ANTH</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>W-WIN-INST</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>KIT-WIN-C</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>win.sill</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>WIN-SILL-PVC</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>W-WIN-SILL</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>KIT-WIN-C</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>win.reveal</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>WIN-REV-PVC</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>W-WIN-REV</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>KIT-WIN-P</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>win.unit</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>WIN-ALU-WOOD</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>W-WIN-INST</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>KIT-WIN-P</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>win.sill</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>WIN-SILL-STONE</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>W-WIN-SILL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>KIT-WIN-P</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>win.reveal</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>WIN-REV-PVC</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>W-WIN-REV</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>KIT-WL-E</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>WL-PNT-LIGHT</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>W-WL-PAINT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>KIT-WL-E</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>econom</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>wall.primer</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>WL-PRIMER</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>W-WL-PRIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>KIT-WL-C</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>WL-PNT-WHITE</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>W-WL-PAINT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>KIT-WL-C</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>comfort</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>wall.primer</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>WL-PRIMER</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>W-WL-PRIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>KIT-WL-P</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>WL-PLASTER-MICRO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>W-WL-PLASTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>KIT-WL-P</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>premium</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>wall.primer</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>WL-PRIMER</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>W-WL-PRIME</t>
         </is>
       </c>
     </row>
@@ -6542,7 +12824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6708,6 +12990,82 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>2026-10-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUP-DR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Демо-поставщик дверей и фурнитуры</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Астана</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUP-WIN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Демо-поставщик окон (изготовление по замеру)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Астана</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -6940,4 +13298,698 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>category_id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>doors</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Двери</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🚪</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Межкомнатные и входные двери: полотно, коробка, наличники, фурнитура</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>windows</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Окна</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🪟</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Окна, подоконники и откосы</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Напольные покрытия</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>▦</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ламинат, SPC, плитка, подложка и плинтус</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>walls</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Стены и отделка</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🖌</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Краска, обои, декоративная штукатурка, панели</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ceiling</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Потолки</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Натяжные и окрашенные потолки</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Электрика</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Розетки, выключатели, кабель, щит</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>plumbing</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Сантехника</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>🚿</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Смесители, унитазы, ванны, душевые</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>furniture</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Мебель</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>🛋</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Кухни, шкафы, кровати, диваны</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>climate</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Кондиционирование</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>❄</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Сплит-системы, трасса и монтаж</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>smarthome</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Умный дом</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>◉</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Выключатели, датчики, хаб</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lighting</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Освещение</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>💡</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Люстры, споты, трековые системы</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>engineering</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Инженерные коммуникации</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>⚙</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Отопление, стояки, электрощит</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>category_id</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>renderer</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>placement</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>primary_slot</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>lesson_steps</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>mistakes</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>door.interior</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>doors</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Межкомнатная дверь</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>🚪</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>door</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>door</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>door.leaf</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Дверной блок: полотно, коробка, наличники с двух сторон, петли, ручка и защёлка. Ставится в готовый проём после чистовой отделки стен и пола.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Проверить проём: ширина полотна + 70–80 мм, высота + 30–40 мм|Собрать коробку под 45° или 90° и закрепить в проёме клиньями|Выставить коробку по уровню и диагоналям, задуть монтажной пеной в 2–3 приёма|Повесить полотно на петли, проверить зазоры 3–4 мм по периметру|Врезать ручку и защёлку, отрегулировать ответную планку|Прибить наличники с двух сторон, при толстой стене — добор</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Монтаж до выравнивания стен и укладки пола — коробку перекосит|Слишком много пены — коробку выгибает внутрь|Не учли толщину стены — наличник не закрывает шов, нужен добор|Перепутали сторону открывания — дверь бьёт в выключатель или мебель</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>door.entrance</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>doors</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Входная дверь</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>🛡</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>entrance</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>entrance</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>entr.door</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Металлический дверной блок с замками, уплотнителем и терморазрывом. Отвечает за безопасность, тепло и шумоизоляцию.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Демонтаж старой двери и очистка проёма|Установка блока на анкеры через коробку (не менее 6–8 точек)|Проверка вертикали, хода полотна и прижима уплотнителя|Запенивание зазора и защита пены от УФ|Отделка откосов</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Крепление только на пену без анкеров|Нет терморазрыва у двери на улицу — конденсат и наледь|Порог ниже чистового пола — сквозняк</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>windows</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Окно</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>🪟</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>win.unit</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Оконный блок: профиль (рама и створки), стеклопакет, фурнитура, подоконник и откосы. Тепло держит связка «профиль + стеклопакет + монтажный шов».</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Замер проёма с учётом четверти|Установка рамы на опорные колодки и анкеры|Монтажный шов: пароизоляция изнутри, пена, паропроницаемая лента снаружи|Подоконник с уклоном 1–2° от окна|Откосы и регулировка фурнитуры</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Пена без защиты лентами — шов промокает и промерзает|Нет зазора под расширение профиля|Подоконник перекрывает радиатор — окно запотевает</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>walls</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Отделка стен</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>🖌</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>wall</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>room_walls</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>wall.finish</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Финишная отделка стен помещения. Площадь считается автоматически: периметр × высота потолка минус двери и окна.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Подготовка: выравнивание и шпаклёвка до нужного класса|Грунт глубокого проникновения|Финиш: окраска в 2 слоя, поклейка обоев, штукатурка или монтаж панелей|Защита углов и стыков</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Красить без грунта — пятна и перерасход|Обои на свежую шпаклёвку без просушки — пузыри|Тёмная краска на плохо выровненной стене подчёркивает дефекты</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>